--- a/Team-Data/2007-08/3-9-2007-08.xlsx
+++ b/Team-Data/2007-08/3-9-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-2.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -760,7 +827,7 @@
         <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
         <v>28</v>
@@ -790,7 +857,7 @@
         <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
         <v>26</v>
@@ -811,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>10.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1224,7 @@
         <v>18</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
         <v>14</v>
@@ -1175,7 +1242,7 @@
         <v>15</v>
       </c>
       <c r="BB4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E5" t="n">
         <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.397</v>
+        <v>0.403</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,49 +1292,49 @@
         <v>36</v>
       </c>
       <c r="J5" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="L5" t="n">
         <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.351</v>
+        <v>0.348</v>
       </c>
       <c r="O5" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.746</v>
+        <v>0.744</v>
       </c>
       <c r="R5" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="S5" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W5" t="n">
         <v>7.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
         <v>5.8</v>
@@ -1276,28 +1343,28 @@
         <v>21.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC5" t="n">
         <v>-2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
         <v>22</v>
@@ -1318,10 +1385,10 @@
         <v>18</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
         <v>19</v>
@@ -1330,22 +1397,22 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV5" t="n">
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1354,10 +1421,10 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1570,7 @@
         <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1719,7 @@
         <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,10 +1728,10 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
         <v>24</v>
@@ -1718,7 +1785,7 @@
         <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1873,13 +1940,13 @@
         <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS8" t="n">
         <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.73</v>
+        <v>0.726</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J9" t="n">
         <v>79.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
@@ -1968,13 +2035,13 @@
         <v>0.373</v>
       </c>
       <c r="O9" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R9" t="n">
         <v>11.6</v>
@@ -1992,7 +2059,7 @@
         <v>11.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X9" t="n">
         <v>5.4</v>
@@ -2001,19 +2068,19 @@
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA9" t="n">
         <v>20.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>98.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC9" t="n">
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,10 +2092,10 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ9" t="n">
         <v>20</v>
@@ -2040,25 +2107,25 @@
         <v>18</v>
       </c>
       <c r="AM9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN9" t="n">
         <v>9</v>
       </c>
       <c r="AO9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
         <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT9" t="n">
         <v>21</v>
@@ -2070,13 +2137,13 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ9" t="n">
         <v>16</v>
@@ -2085,10 +2152,10 @@
         <v>22</v>
       </c>
       <c r="BB9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2240,7 +2307,7 @@
         <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>5</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2389,16 +2456,16 @@
         <v>5</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
         <v>11</v>
@@ -2434,7 +2501,7 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
         <v>4</v>
@@ -2452,7 +2519,7 @@
         <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
@@ -2592,7 +2659,7 @@
         <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
         <v>21</v>
@@ -2604,13 +2671,13 @@
         <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV12" t="n">
         <v>27</v>
@@ -2628,7 +2695,7 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2786,10 +2853,10 @@
         <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU13" t="n">
         <v>15</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="n">
         <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.698</v>
+        <v>0.71</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2863,7 +2930,7 @@
         <v>39.5</v>
       </c>
       <c r="J14" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.479</v>
@@ -2875,31 +2942,31 @@
         <v>20.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O14" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="P14" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R14" t="n">
         <v>10.8</v>
       </c>
       <c r="S14" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W14" t="n">
         <v>8.199999999999999</v>
@@ -2908,22 +2975,22 @@
         <v>5.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA14" t="n">
         <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.2</v>
+        <v>108.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2947,10 +3014,10 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
         <v>10</v>
@@ -2962,7 +3029,7 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
@@ -2971,13 +3038,13 @@
         <v>1</v>
       </c>
       <c r="AT14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW14" t="n">
         <v>6</v>
@@ -2989,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -2998,7 +3065,7 @@
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG15" t="n">
         <v>28</v>
@@ -3168,7 +3235,7 @@
         <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3308,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3341,7 +3408,7 @@
         <v>22</v>
       </c>
       <c r="AV16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
         <v>18</v>
@@ -3350,7 +3417,7 @@
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3458,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>0.365</v>
+        <v>0.371</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J17" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K17" t="n">
         <v>0.449</v>
@@ -3418,16 +3485,16 @@
         <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O17" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q17" t="n">
         <v>0.742</v>
@@ -3436,16 +3503,16 @@
         <v>12.3</v>
       </c>
       <c r="S17" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="T17" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U17" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V17" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
         <v>6.5</v>
@@ -3454,7 +3521,7 @@
         <v>4.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z17" t="n">
         <v>21.4</v>
@@ -3466,25 +3533,25 @@
         <v>96</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.5</v>
+        <v>-6.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
       </c>
       <c r="AF17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
         <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>14</v>
@@ -3499,10 +3566,10 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO17" t="n">
         <v>24</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>25</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -3517,7 +3584,7 @@
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AU17" t="n">
         <v>19</v>
@@ -3541,10 +3608,10 @@
         <v>19</v>
       </c>
       <c r="BB17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3672,7 +3739,7 @@
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
@@ -3681,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -3845,13 +3912,13 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
       </c>
       <c r="AJ19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -3863,7 +3930,7 @@
         <v>17</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4027,7 +4094,7 @@
         <v>5</v>
       </c>
       <c r="AH20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
@@ -4087,10 +4154,10 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -4227,10 +4294,10 @@
         <v>16</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP21" t="n">
         <v>10</v>
@@ -4272,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF22" t="n">
         <v>11</v>
@@ -4397,7 +4464,7 @@
         <v>12</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23" t="n">
         <v>33</v>
       </c>
       <c r="G23" t="n">
-        <v>0.476</v>
+        <v>0.468</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.464</v>
+        <v>0.461</v>
       </c>
       <c r="L23" t="n">
         <v>3.6</v>
@@ -4516,16 +4583,16 @@
         <v>0.32</v>
       </c>
       <c r="O23" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P23" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.703</v>
+        <v>0.702</v>
       </c>
       <c r="R23" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S23" t="n">
         <v>29</v>
@@ -4534,7 +4601,7 @@
         <v>42</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V23" t="n">
         <v>15</v>
@@ -4543,10 +4610,10 @@
         <v>8.6</v>
       </c>
       <c r="X23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y23" t="n">
         <v>4.8</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>4.7</v>
       </c>
       <c r="Z23" t="n">
         <v>19.8</v>
@@ -4555,16 +4622,16 @@
         <v>20.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF23" t="n">
         <v>17</v>
@@ -4573,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4582,7 +4649,7 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4594,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
         <v>13</v>
@@ -4615,7 +4682,7 @@
         <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>5</v>
@@ -4633,7 +4700,7 @@
         <v>21</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E24" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" t="n">
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.651</v>
+        <v>0.645</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4689,13 +4756,13 @@
         <v>0.492</v>
       </c>
       <c r="L24" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O24" t="n">
         <v>18.5</v>
@@ -4704,46 +4771,46 @@
         <v>23.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="R24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S24" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T24" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="U24" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="V24" t="n">
         <v>14.2</v>
       </c>
       <c r="W24" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X24" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Y24" t="n">
         <v>3.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.2</v>
+        <v>109.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>8</v>
@@ -4755,7 +4822,7 @@
         <v>8</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>2</v>
@@ -4776,7 +4843,7 @@
         <v>4</v>
       </c>
       <c r="AO24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP24" t="n">
         <v>23</v>
@@ -4788,16 +4855,16 @@
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
         <v>21</v>
@@ -4806,7 +4873,7 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4995,7 @@
         <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4964,7 +5031,7 @@
         <v>24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" t="n">
         <v>35</v>
       </c>
       <c r="G26" t="n">
-        <v>0.444</v>
+        <v>0.435</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
         <v>79.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M26" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O26" t="n">
         <v>22</v>
       </c>
       <c r="P26" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R26" t="n">
         <v>10.4</v>
@@ -5083,13 +5150,13 @@
         <v>19</v>
       </c>
       <c r="V26" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="W26" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y26" t="n">
         <v>5.6</v>
@@ -5098,16 +5165,16 @@
         <v>22.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB26" t="n">
-        <v>101.6</v>
+        <v>101.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,10 +5186,10 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
@@ -5146,7 +5213,7 @@
         <v>5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR26" t="n">
         <v>22</v>
@@ -5155,7 +5222,7 @@
         <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
@@ -5164,7 +5231,7 @@
         <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
         <v>25</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -5211,37 +5278,37 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" t="n">
         <v>43</v>
       </c>
       <c r="F27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27" t="n">
-        <v>0.694</v>
+        <v>0.705</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J27" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L27" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M27" t="n">
         <v>20.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="O27" t="n">
         <v>16.9</v>
@@ -5262,13 +5329,13 @@
         <v>41.6</v>
       </c>
       <c r="U27" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="V27" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
@@ -5283,13 +5350,13 @@
         <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="AC27" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>4</v>
@@ -5301,16 +5368,16 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL27" t="n">
         <v>6</v>
@@ -5328,7 +5395,7 @@
         <v>26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
         <v>24</v>
@@ -5340,7 +5407,7 @@
         <v>17</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AV27" t="n">
         <v>5</v>
@@ -5361,10 +5428,10 @@
         <v>25</v>
       </c>
       <c r="BB27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G28" t="n">
-        <v>0.254</v>
+        <v>0.258</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,43 +5478,43 @@
         <v>37.7</v>
       </c>
       <c r="J28" t="n">
-        <v>84.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.444</v>
+        <v>0.442</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M28" t="n">
         <v>12</v>
       </c>
       <c r="N28" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O28" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.765</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S28" t="n">
         <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U28" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V28" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W28" t="n">
         <v>6.4</v>
@@ -5456,7 +5523,7 @@
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z28" t="n">
         <v>20.8</v>
@@ -5465,13 +5532,13 @@
         <v>19.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC28" t="n">
         <v>-7.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5483,7 +5550,7 @@
         <v>27</v>
       </c>
       <c r="AH28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5501,19 +5568,19 @@
         <v>29</v>
       </c>
       <c r="AN28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP28" t="n">
         <v>25</v>
       </c>
       <c r="AQ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR28" t="n">
         <v>11</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>12</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5522,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
@@ -5537,7 +5604,7 @@
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F29" t="n">
         <v>28</v>
       </c>
       <c r="G29" t="n">
-        <v>0.548</v>
+        <v>0.541</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J29" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K29" t="n">
         <v>0.466</v>
@@ -5602,10 +5669,10 @@
         <v>7.5</v>
       </c>
       <c r="M29" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.406</v>
+        <v>0.407</v>
       </c>
       <c r="O29" t="n">
         <v>16.8</v>
@@ -5614,16 +5681,16 @@
         <v>20.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R29" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U29" t="n">
         <v>23.1</v>
@@ -5647,13 +5714,13 @@
         <v>18.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.4</v>
+        <v>100.2</v>
       </c>
       <c r="AC29" t="n">
         <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5665,19 +5732,19 @@
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK29" t="n">
         <v>6</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5698,7 +5765,7 @@
         <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
         <v>27</v>
@@ -5716,7 +5783,7 @@
         <v>27</v>
       </c>
       <c r="AY29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ29" t="n">
         <v>8</v>
@@ -5725,7 +5792,7 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -5880,10 +5947,10 @@
         <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6047,7 +6114,7 @@
         <v>12</v>
       </c>
       <c r="AN31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6056,7 +6123,7 @@
         <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR31" t="n">
         <v>5</v>
@@ -6074,10 +6141,10 @@
         <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY31" t="n">
         <v>8</v>
@@ -6089,7 +6156,7 @@
         <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-9-2007-08</t>
+          <t>2008-03-09</t>
         </is>
       </c>
     </row>
